--- a/scenarios/02_mike_detector_engineer/2.3_ipc_impact_on_mtf/outputs/ipc_sweep_results.xlsx
+++ b/scenarios/02_mike_detector_engineer/2.3_ipc_impact_on_mtf/outputs/ipc_sweep_results.xlsx
@@ -454,15 +454,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,27 +482,37 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>MTF_IPC [—]</t>
+          <t>System MTF@Nyq [—]</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>System MTF@Nyq [—]</t>
+          <t>EE 1×1 [—]</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>EE 1×1 [—]</t>
+          <t>EE 3×3 [—]</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>EE 3×3 [—]</t>
+          <t>RER [—]</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
+          <t>FWHM [µm]</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>SNR [—]</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>NEDT [K]</t>
         </is>
       </c>
     </row>
@@ -508,1020 +520,1326 @@
       <c r="A4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>0.4223</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>0.6365</v>
+      <c r="B4" s="4" t="n">
+        <v>0.2532</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.4699</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6014</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>0.4206</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>0.634</v>
+      <c r="B5" s="4" t="n">
+        <v>0.2531</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.4699</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6014</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>0.992</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>0.4189</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>0.6315</v>
+      <c r="B6" s="4" t="n">
+        <v>0.2531</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.4699</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6014</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>0.988</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>0.4172</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>0.6289</v>
+      <c r="B7" s="4" t="n">
+        <v>0.2531</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.4698</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6014</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>0.984</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>0.4155</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>0.6264</v>
+      <c r="B8" s="4" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.4698</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6014</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>0.4138</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>0.6238</v>
+      <c r="B9" s="4" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.4698</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>0.976</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>0.4121</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>0.6213</v>
+      <c r="B10" s="4" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.4697</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="B11" s="3" t="n">
-        <v>0.972</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>0.4104</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>0.6187</v>
+      <c r="B11" s="4" t="n">
+        <v>0.2529</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.4697</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>0.968</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>0.4088</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>0.6162</v>
+      <c r="B12" s="4" t="n">
+        <v>0.2529</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.4697</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="B13" s="3" t="n">
-        <v>0.964</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>0.4071</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>0.6136</v>
+      <c r="B13" s="4" t="n">
+        <v>0.2528</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.4696</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6012</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="3" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>0.4054</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>0.6111</v>
+      <c r="B14" s="4" t="n">
+        <v>0.2528</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.4696</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6012</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="B15" s="3" t="n">
-        <v>0.956</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>0.4037</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>0.6085</v>
+      <c r="B15" s="4" t="n">
+        <v>0.2528</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.4696</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6012</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>0.952</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>0.606</v>
+      <c r="B16" s="4" t="n">
+        <v>0.2527</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.4695</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6012</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="B17" s="3" t="n">
-        <v>0.948</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>0.4003</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>0.6034</v>
+      <c r="B17" s="4" t="n">
+        <v>0.2527</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.4695</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6012</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="B18" s="3" t="n">
-        <v>0.944</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>0.3986</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>0.6009</v>
+      <c r="B18" s="4" t="n">
+        <v>0.2527</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.4695</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6011</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="B19" s="3" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>0.3969</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>0.5984</v>
+      <c r="B19" s="4" t="n">
+        <v>0.2526</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0.4694</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6011</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>0.9360000000000001</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>0.3952</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>0.5958</v>
+      <c r="B20" s="4" t="n">
+        <v>0.2526</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>0.4694</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6011</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="B21" s="3" t="n">
-        <v>0.9320000000000001</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>0.3936</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>0.5933</v>
+      <c r="B21" s="4" t="n">
+        <v>0.2526</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0.4694</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6011</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="B22" s="3" t="n">
-        <v>0.928</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>0.3919</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>0.5907</v>
+      <c r="B22" s="4" t="n">
+        <v>0.2525</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.4693</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.601</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="B23" s="3" t="n">
-        <v>0.924</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>0.3902</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>0.5881999999999999</v>
+      <c r="B23" s="4" t="n">
+        <v>0.2525</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>0.4693</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.601</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B24" s="3" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>0.3885</v>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>0.5856</v>
+      <c r="B24" s="4" t="n">
+        <v>0.2525</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.4693</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.601</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="B25" s="3" t="n">
-        <v>0.916</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>0.3868</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>0.5831</v>
+      <c r="B25" s="4" t="n">
+        <v>0.2524</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>0.4692</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.601</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="B26" s="3" t="n">
-        <v>0.912</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>0.3851</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>0.5805</v>
+      <c r="B26" s="4" t="n">
+        <v>0.2524</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>0.4692</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.601</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="B27" s="3" t="n">
-        <v>0.908</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>0.3834</v>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>0.578</v>
+      <c r="B27" s="4" t="n">
+        <v>0.2524</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>0.4692</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6009</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="B28" s="3" t="n">
-        <v>0.904</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>0.3817</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>0.5754</v>
+      <c r="B28" s="4" t="n">
+        <v>0.2523</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>0.4691</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6009</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="B29" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>0.5729</v>
+      <c r="B29" s="4" t="n">
+        <v>0.2523</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>0.4691</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6009</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="B30" s="3" t="n">
-        <v>0.896</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>0.3783</v>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>0.5703</v>
+      <c r="B30" s="4" t="n">
+        <v>0.2523</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>0.4691</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6009</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="B31" s="3" t="n">
-        <v>0.892</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>0.3767</v>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>0.5678</v>
+      <c r="B31" s="4" t="n">
+        <v>0.2522</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6008</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="B32" s="3" t="n">
-        <v>0.888</v>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>0.5653</v>
+      <c r="B32" s="4" t="n">
+        <v>0.2522</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6008</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="B33" s="3" t="n">
-        <v>0.884</v>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>0.3733</v>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>0.5627</v>
+      <c r="B33" s="4" t="n">
+        <v>0.2522</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6008</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B34" s="3" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>0.3716</v>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>0.5602</v>
+      <c r="B34" s="4" t="n">
+        <v>0.2521</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>0.4689</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6008</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="B35" s="3" t="n">
-        <v>0.876</v>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>0.3699</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>0.5576</v>
+      <c r="B35" s="4" t="n">
+        <v>0.2521</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>0.4689</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6008</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="B36" s="3" t="n">
-        <v>0.872</v>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>0.3682</v>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>0.5551</v>
+      <c r="B36" s="4" t="n">
+        <v>0.2521</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>0.4689</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6007</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="B37" s="3" t="n">
-        <v>0.868</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>0.3665</v>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>0.5525</v>
+      <c r="B37" s="4" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>0.4688</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6007</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="B38" s="3" t="n">
-        <v>0.864</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>0.3648</v>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>0.55</v>
+      <c r="B38" s="4" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>0.4688</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6007</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="B39" s="3" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>0.3631</v>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>0.5474</v>
+      <c r="B39" s="4" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>0.4688</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6007</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>536.27</v>
+        <v>21.8</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="B40" s="3" t="n">
-        <v>0.856</v>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>0.3615</v>
-      </c>
-      <c r="D40" s="5" t="n">
-        <v>0.5449000000000001</v>
+      <c r="B40" s="4" t="n">
+        <v>0.2519</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>0.4687</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6006</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>536.27</v>
+        <v>21.9</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
         <v>3.7</v>
       </c>
-      <c r="B41" s="3" t="n">
-        <v>0.852</v>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>0.3598</v>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>0.5423</v>
+      <c r="B41" s="4" t="n">
+        <v>0.2519</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>0.4687</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6006</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>536.27</v>
+        <v>21.9</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="B42" s="3" t="n">
-        <v>0.848</v>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>0.3581</v>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>0.5397999999999999</v>
+      <c r="B42" s="4" t="n">
+        <v>0.2518</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6006</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>536.27</v>
+        <v>21.9</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="B43" s="3" t="n">
-        <v>0.844</v>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>0.3564</v>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>0.5372</v>
+      <c r="B43" s="4" t="n">
+        <v>0.2518</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6006</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>536.27</v>
+        <v>21.9</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B44" s="3" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>0.3547</v>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>0.5347</v>
+      <c r="B44" s="4" t="n">
+        <v>0.2518</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6006</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>536.27</v>
+        <v>21.9</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="B45" s="3" t="n">
-        <v>0.836</v>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>0.353</v>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>0.5322</v>
+      <c r="B45" s="4" t="n">
+        <v>0.2517</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>0.4685</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6005</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>536.27</v>
+        <v>21.9</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="B46" s="3" t="n">
-        <v>0.832</v>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>0.3513</v>
-      </c>
-      <c r="D46" s="5" t="n">
-        <v>0.5296</v>
+      <c r="B46" s="4" t="n">
+        <v>0.2517</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>0.4685</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6005</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>536.27</v>
+        <v>21.9</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
         <v>4.3</v>
       </c>
-      <c r="B47" s="3" t="n">
-        <v>0.828</v>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>0.3496</v>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>0.5271</v>
+      <c r="B47" s="4" t="n">
+        <v>0.2517</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>0.4685</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6005</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>536.27</v>
+        <v>21.9</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="B48" s="3" t="n">
-        <v>0.824</v>
-      </c>
-      <c r="C48" s="4" t="n">
-        <v>0.3479</v>
-      </c>
-      <c r="D48" s="5" t="n">
-        <v>0.5245</v>
+      <c r="B48" s="4" t="n">
+        <v>0.2516</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>0.4684</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6005</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>536.27</v>
+        <v>21.9</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="B49" s="3" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>0.3463</v>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>0.522</v>
+      <c r="B49" s="4" t="n">
+        <v>0.2516</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>0.4684</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6004</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>536.27</v>
+        <v>21.9</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="B50" s="3" t="n">
-        <v>0.8159999999999999</v>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>0.3446</v>
-      </c>
-      <c r="D50" s="5" t="n">
-        <v>0.5194</v>
+      <c r="B50" s="4" t="n">
+        <v>0.2516</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>0.4684</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6004</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>536.27</v>
+        <v>21.9</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="B51" s="3" t="n">
-        <v>0.8120000000000001</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>0.3429</v>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>0.5169</v>
+      <c r="B51" s="4" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>0.4683</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6004</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>536.27</v>
+        <v>21.9</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="B52" s="3" t="n">
-        <v>0.8080000000000001</v>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>0.3412</v>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>0.5143</v>
+      <c r="B52" s="4" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>0.4683</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6004</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>536.27</v>
+        <v>21.9</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="B53" s="3" t="n">
-        <v>0.804</v>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>0.3395</v>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>0.5118</v>
+      <c r="B53" s="4" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>0.4683</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6004</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>536.27</v>
+        <v>21.9</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B54" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>0.3378</v>
-      </c>
-      <c r="D54" s="5" t="n">
-        <v>0.5092</v>
+      <c r="B54" s="4" t="n">
+        <v>0.2514</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>0.4682</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0.8822</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>0.8893</v>
+        <v>0.6002999999999999</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>536.27</v>
+        <v>21.9</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>586.4299999999999</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>0.0484</v>
       </c>
     </row>
   </sheetData>
@@ -1572,7 +1890,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Model MTF@Nyq [—]</t>
+          <t>RADIANT MTF@Nyq [—]</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -1587,7 +1905,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Model EE 1×1 [—]</t>
+          <t>RADIANT EE 1×1 [—]</t>
         </is>
       </c>
     </row>
@@ -1604,16 +1922,16 @@
         <v>0.38</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.402</v>
+        <v>0.2527</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-0.022</v>
+        <v>0.1273</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0.82</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.606</v>
+        <v>0.4695</v>
       </c>
     </row>
     <row r="5">
@@ -1629,16 +1947,16 @@
         <v>0.34</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.3919</v>
+        <v>0.2525</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-0.0519</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0.78</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.5907</v>
+        <v>0.4693</v>
       </c>
     </row>
     <row r="6">
@@ -1654,16 +1972,16 @@
         <v>0.3</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.3834</v>
+        <v>0.2524</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-0.0834</v>
+        <v>0.0476</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0.74</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.578</v>
+        <v>0.4692</v>
       </c>
     </row>
     <row r="7">
@@ -1679,16 +1997,16 @@
         <v>0.26</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.375</v>
+        <v>0.2522</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-0.115</v>
+        <v>0.0078</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.5653</v>
+        <v>0.469</v>
       </c>
     </row>
     <row r="8">
@@ -1704,16 +2022,16 @@
         <v>0.21</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.3631</v>
+        <v>0.252</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>-0.1531</v>
+        <v>-0.042</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0.65</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.5474</v>
+        <v>0.4688</v>
       </c>
     </row>
   </sheetData>
@@ -1727,7 +2045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1749,7 +2067,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.4223</t>
+          <t>0.2532</t>
         </is>
       </c>
     </row>
@@ -1761,7 +2079,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>536.27</t>
+          <t>586.43</t>
         </is>
       </c>
     </row>
@@ -1773,149 +2091,233 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.6365</t>
+          <t>0.4699</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Baseline RER [—]</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.6014</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>MTF requirement [—]</t>
+          <t>Baseline FWHM [µm]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>≥ 0.15</t>
+          <t>21.8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>EE 1×1 requirement [—]</t>
+          <t>GSD (cross-track) [m]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>≥ 0.6</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>SNR requirement [—]</t>
+          <t>Q (sampling parameter) [—]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>≥ 100</t>
+          <t>0.944</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>NEDT [K]</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.0484</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Max IPC for MTF requirement [%]</t>
+          <t>NIIRS [—]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>&gt; 5.0</t>
+          <t>4.61</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Max IPC for EE requirement [%]</t>
+          <t>Strehl ratio [—]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.0000</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Binding constraint</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>EE 1×1</t>
-        </is>
-      </c>
+      <c r="A13" s="7" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Max tolerable IPC [%]</t>
+          <t>MTF requirement [—]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>≥ 0.15</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>EE 1×1 requirement [—]</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>≥ 0.6</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Vendor typical IPC [%]</t>
+          <t>SNR requirement [—]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>≥ 100</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Vendor typical vs. limit</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+      <c r="A17" s="7" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Vendor max IPC [%]</t>
+          <t>Max IPC for MTF requirement [%]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>&gt; 5.0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
+          <t>Max IPC for EE requirement [%]</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>&gt; 5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Binding constraint</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>EE 1×1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Max tolerable IPC [%]</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>&gt; 5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Vendor typical IPC [%]</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Vendor typical vs. limit</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Vendor max IPC [%]</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
           <t>Vendor max vs. limit</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
